--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487848_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487848_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8359</v>
+        <v>5.4263</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6915</v>
+        <v>1.37</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1444</v>
+        <v>4.0563</v>
       </c>
       <c r="G2" t="n">
         <v>2.0197</v>
@@ -610,13 +610,13 @@
         <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>0.839</v>
+        <v>0.4294</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1239</v>
+        <v>-0.1976</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7151</v>
+        <v>0.627</v>
       </c>
       <c r="V2" t="n">
         <v>2.3528</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3331</v>
+        <v>1.3888</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5936</v>
+        <v>0.0493</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9267</v>
+        <v>1.3395</v>
       </c>
       <c r="G3" t="n">
         <v>-0.06809999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>0.55</v>
+        <v>0.6058</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9134</v>
+        <v>-0.2705</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4634</v>
+        <v>0.8762</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8137</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2097</v>
+        <v>1.2292</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2383</v>
+        <v>-1.324</v>
       </c>
       <c r="F4" t="n">
-        <v>2.448</v>
+        <v>2.5532</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9858</v>
+        <v>0.3775</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.6478</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.57</v>
+        <v>-1.2703</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1941</v>
+        <v>0.3981</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1639</v>
+        <v>1.7093</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0302</v>
+        <v>-1.3112</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1798</v>
+        <v>-0.0206</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4203</v>
+        <v>-0.0614</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6002</v>
+        <v>0.0408</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2081</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>-4.1624</v>
       </c>
       <c r="R4" t="n">
         <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5898</v>
+        <v>-0.1941</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9786</v>
+        <v>-0.4786</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5685</v>
+        <v>0.2845</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3975</v>
+        <v>2.9188</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6275</v>
+        <v>2.9188</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1499</v>
+        <v>1.0408</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1097</v>
+        <v>-0.7025</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2596</v>
+        <v>1.7433</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3775</v>
+        <v>-0.9858</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6478</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2703</v>
+        <v>-1.57</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3981</v>
+        <v>0.1941</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7093</v>
+        <v>0.1639</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3112</v>
+        <v>0.0302</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0206</v>
+        <v>-1.1798</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0614</v>
+        <v>0.4203</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0408</v>
+        <v>-1.6002</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1624</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
         <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2734</v>
+        <v>0.421</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2643</v>
+        <v>-0.4429</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0091</v>
+        <v>0.8639</v>
       </c>
       <c r="V5" t="n">
-        <v>2.9188</v>
+        <v>1.3975</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9188</v>
+        <v>1.6275</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.916</v>
+        <v>0.5262</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5962</v>
+        <v>-1.1405</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3198</v>
+        <v>1.6667</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6491</v>
+        <v>-1.6619</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4393</v>
+        <v>-0.243</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2098</v>
+        <v>-1.419</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6368</v>
+        <v>-1.221</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.676</v>
+        <v>-1.3328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>0.1118</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0123</v>
+        <v>-0.4409</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2367</v>
+        <v>1.0898</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.249</v>
+        <v>-1.5308</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1489</v>
+        <v>0.337</v>
       </c>
       <c r="T6" t="n">
-        <v>1.233</v>
+        <v>0.0805</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0842</v>
+        <v>0.2564</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4762</v>
+        <v>0.3612</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1833</v>
+        <v>-0.0467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2929</v>
+        <v>0.4079</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7678</v>
+        <v>-0.6491</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0854</v>
+        <v>-0.4393</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8533</v>
+        <v>-0.2098</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0494</v>
+        <v>-0.6368</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0937</v>
+        <v>-0.676</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1431</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2816</v>
+        <v>-0.0123</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0083</v>
+        <v>0.2367</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2898</v>
+        <v>-0.249</v>
       </c>
       <c r="P7" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3679</v>
+        <v>0.594</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6458</v>
+        <v>0.5901</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2779</v>
+        <v>0.0039</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.1665</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3548</v>
+        <v>-0.5668</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2557</v>
+        <v>0.7333</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6619</v>
+        <v>-0.7678</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.243</v>
+        <v>1.0854</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.419</v>
+        <v>-1.8533</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.221</v>
+        <v>-1.0494</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3328</v>
+        <v>1.0937</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1118</v>
+        <v>-2.1431</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4409</v>
+        <v>0.2816</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0898</v>
+        <v>-0.0083</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5308</v>
+        <v>0.2898</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2884</v>
+        <v>0.0582</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1338</v>
+        <v>-0.1043</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1546</v>
+        <v>0.1625</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.23</v>
+        <v>0.4599</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.7795</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9905</v>
+        <v>-1.2048</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4547</v>
+        <v>0.4253</v>
       </c>
       <c r="G9" t="n">
         <v>-2.789</v>
@@ -1156,13 +1156,13 @@
         <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9806</v>
+        <v>0.7369</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4501</v>
+        <v>0.2358</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5305</v>
+        <v>0.5011</v>
       </c>
       <c r="V9" t="n">
         <v>2.1051</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0252</v>
+        <v>-1.3617</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4382</v>
+        <v>-3.0096</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4129</v>
+        <v>1.6478</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3617</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8716</v>
+        <v>-0.2081</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7829</v>
+        <v>-0.3543</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0887</v>
+        <v>0.1462</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3986</v>
+        <v>-2.1358</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1175</v>
+        <v>-2.796</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7189</v>
+        <v>0.6602</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1144</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4671</v>
+        <v>0.7299</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0033</v>
+        <v>0.3182</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4704</v>
+        <v>0.4117</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8621</v>
+        <v>5.862</v>
       </c>
       <c r="E12" t="n">
         <v>-9.371599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>15.2336</v>
+        <v>15.2335</v>
       </c>
       <c r="G12" t="n">
         <v>-10.0006</v>
@@ -1381,7 +1381,7 @@
         <v>-5.490500000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1622</v>
+        <v>4.162199999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.5278</v>
@@ -1390,13 +1390,13 @@
         <v>17.6899</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5099</v>
+        <v>3.510000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6234999999999999</v>
+        <v>-0.6235999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>4.133399999999999</v>
+        <v>4.1334</v>
       </c>
       <c r="V12" t="n">
         <v>8.1904</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3748</v>
+        <v>4.6288</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5347</v>
+        <v>0.6419</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8401</v>
+        <v>3.9869</v>
       </c>
       <c r="G13" t="n">
         <v>5.9193</v>
@@ -1468,13 +1468,13 @@
         <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4612</v>
+        <v>-0.2073</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.721</v>
+        <v>-0.6138</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2597</v>
+        <v>0.4065</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2914</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.455</v>
+        <v>1.6605</v>
       </c>
       <c r="E14" t="n">
         <v>-0.889</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3441</v>
+        <v>2.5496</v>
       </c>
       <c r="G14" t="n">
         <v>0.5012</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2949</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-0.3295</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0346</v>
+        <v>0.2401</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4323</v>
+        <v>0.8466</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8782</v>
+        <v>-1.1997</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3105</v>
+        <v>2.0463</v>
       </c>
       <c r="G15" t="n">
         <v>1.6825</v>
@@ -1624,13 +1624,13 @@
         <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2929</v>
+        <v>-0.2928</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2023</v>
+        <v>-0.5238</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4953</v>
+        <v>0.231</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6089</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5318000000000001</v>
+        <v>-1.8375</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1406</v>
+        <v>0.963</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2442</v>
+        <v>0.2768</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4245</v>
+        <v>-2.5243</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6686</v>
+        <v>2.8011</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0784</v>
+        <v>0.0486</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-1.3564</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0784</v>
+        <v>1.405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3225</v>
+        <v>0.2282</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4245</v>
+        <v>-1.1679</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.747</v>
+        <v>1.3961</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3647</v>
+        <v>-0.5676</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4534</v>
+        <v>-1.2025</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8181</v>
+        <v>0.6349</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.804</v>
+        <v>-0.9788</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2661</v>
+        <v>0.1032</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4621</v>
+        <v>-1.0819</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2768</v>
+        <v>-0.2442</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.5243</v>
+        <v>0.4245</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8011</v>
+        <v>-0.6686</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0486</v>
+        <v>0.0784</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3564</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.405</v>
+        <v>0.0784</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2282</v>
+        <v>-0.3225</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1679</v>
+        <v>0.4245</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3961</v>
+        <v>-0.747</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4971</v>
+        <v>-0.7346</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6311</v>
+        <v>0.0248</v>
       </c>
       <c r="U17" t="n">
-        <v>1.134</v>
+        <v>-0.7594</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2274</v>
+        <v>-1.0601</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8978</v>
+        <v>-2.1121</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6703</v>
+        <v>1.052</v>
       </c>
       <c r="G18" t="n">
         <v>0.2545</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6713</v>
+        <v>-0.504</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2829</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6028</v>
+        <v>-0.2211</v>
       </c>
       <c r="V18" t="n">
         <v>0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.9803</v>
+        <v>-4.4239</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2906</v>
+        <v>-1.9692</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6896</v>
+        <v>-2.4548</v>
       </c>
       <c r="G19" t="n">
         <v>0.1552</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7817</v>
+        <v>-1.2254</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9786</v>
+        <v>-0.6572</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8031</v>
+        <v>-0.5682</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1051</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5036</v>
+        <v>-5.6607</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.0784</v>
+        <v>-7.9712</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5747</v>
+        <v>2.3105</v>
       </c>
       <c r="G20" t="n">
         <v>1.4551</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2682</v>
+        <v>0.1111</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.5486</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.6597</v>
       </c>
       <c r="V20" t="n">
         <v>-3.2726</v>
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.862099999999998</v>
+        <v>-5.8621</v>
       </c>
       <c r="E21" t="n">
         <v>-15.2336</v>
@@ -2059,7 +2059,7 @@
         <v>10.0004</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.653900000000001</v>
+        <v>-2.6539</v>
       </c>
       <c r="I21" t="n">
         <v>12.6546</v>
@@ -2080,7 +2080,7 @@
         <v>-2.2676</v>
       </c>
       <c r="O21" t="n">
-        <v>7.164199999999999</v>
+        <v>7.1642</v>
       </c>
       <c r="P21" t="n">
         <v>-4.162299999999999</v>
@@ -2092,10 +2092,10 @@
         <v>13.5277</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.5098</v>
+        <v>-3.51</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.1333</v>
+        <v>-4.1335</v>
       </c>
       <c r="U21" t="n">
         <v>0.6234999999999999</v>
